--- a/api/1/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/1/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5551" uniqueCount="3680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5575" uniqueCount="3696">
   <si>
     <t>code</t>
   </si>
@@ -9682,6 +9682,12 @@
     <t>Tech2Peace</t>
   </si>
   <si>
+    <t>XM-DAC-47062</t>
+  </si>
+  <si>
+    <t>International Institute of Tropical Agriculture (IITA)</t>
+  </si>
+  <si>
     <t>JO-COA-0301-57112</t>
   </si>
   <si>
@@ -10489,6 +10495,12 @@
     <t>Village Infrastructure Angels</t>
   </si>
   <si>
+    <t>GB-COH-05380206</t>
+  </si>
+  <si>
+    <t>Joint Nature Conservation Committee</t>
+  </si>
+  <si>
     <t>GB-COH-02525806</t>
   </si>
   <si>
@@ -10903,6 +10915,12 @@
     <t>Soul City Institute</t>
   </si>
   <si>
+    <t>ZA-CIP-2007-012585-08</t>
+  </si>
+  <si>
+    <t>Reach Digital Health NPC</t>
+  </si>
+  <si>
     <t>US-EIN-53-0196603</t>
   </si>
   <si>
@@ -10975,6 +10993,12 @@
     <t>Design without Borders Africa</t>
   </si>
   <si>
+    <t>XI-DUNS-499432771</t>
+  </si>
+  <si>
+    <t>Navrongo Health Research Centre</t>
+  </si>
+  <si>
     <t>US-SAM-VJ8RGVMEPAT7</t>
   </si>
   <si>
@@ -11023,6 +11047,12 @@
     <t>Tax Justice Network</t>
   </si>
   <si>
+    <t>ZA-CIP-2022-449689-08</t>
+  </si>
+  <si>
+    <t>Energy Council of South Africa</t>
+  </si>
+  <si>
     <t>FR-INSEE-93282389100019</t>
   </si>
   <si>
@@ -11039,6 +11069,24 @@
   </si>
   <si>
     <t>Clim-Eat</t>
+  </si>
+  <si>
+    <t>SL-NRA-1136607-8</t>
+  </si>
+  <si>
+    <t>Institute of Gender and Children's Health Research</t>
+  </si>
+  <si>
+    <t>SL-OARG-2420280</t>
+  </si>
+  <si>
+    <t>Centre of Dialogue on Human Settlement and Poverty Alleviation (CODOHSAPA)</t>
+  </si>
+  <si>
+    <t>GB-COH-08195029</t>
+  </si>
+  <si>
+    <t>Environmental Finance Limited, trading as Finance Earth</t>
   </si>
   <si>
     <t>US-EIN-52-1780162</t>
@@ -11385,7 +11433,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1849"/>
+  <dimension ref="A1:G1857"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -29225,7 +29273,7 @@
         <v>3224</v>
       </c>
       <c r="B1621" t="s">
-        <v>3217</v>
+        <v>3225</v>
       </c>
       <c r="D1621" t="s">
         <v>9</v>
@@ -29233,10 +29281,10 @@
     </row>
     <row r="1622" spans="1:4">
       <c r="A1622" t="s">
-        <v>3225</v>
+        <v>3226</v>
       </c>
       <c r="B1622" t="s">
-        <v>3226</v>
+        <v>3217</v>
       </c>
       <c r="D1622" t="s">
         <v>9</v>
@@ -31722,7 +31770,7 @@
         <v>3677</v>
       </c>
       <c r="B1848" t="s">
-        <v>3266</v>
+        <v>3678</v>
       </c>
       <c r="D1848" t="s">
         <v>9</v>
@@ -31730,12 +31778,100 @@
     </row>
     <row r="1849" spans="1:4">
       <c r="A1849" t="s">
-        <v>3678</v>
+        <v>3679</v>
       </c>
       <c r="B1849" t="s">
-        <v>3679</v>
+        <v>3680</v>
       </c>
       <c r="D1849" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1850" spans="1:4">
+      <c r="A1850" t="s">
+        <v>3681</v>
+      </c>
+      <c r="B1850" t="s">
+        <v>3682</v>
+      </c>
+      <c r="D1850" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1851" spans="1:4">
+      <c r="A1851" t="s">
+        <v>3683</v>
+      </c>
+      <c r="B1851" t="s">
+        <v>3684</v>
+      </c>
+      <c r="D1851" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1852" spans="1:4">
+      <c r="A1852" t="s">
+        <v>3685</v>
+      </c>
+      <c r="B1852" t="s">
+        <v>3686</v>
+      </c>
+      <c r="D1852" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1853" spans="1:4">
+      <c r="A1853" t="s">
+        <v>3687</v>
+      </c>
+      <c r="B1853" t="s">
+        <v>3688</v>
+      </c>
+      <c r="D1853" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1854" spans="1:4">
+      <c r="A1854" t="s">
+        <v>3689</v>
+      </c>
+      <c r="B1854" t="s">
+        <v>3690</v>
+      </c>
+      <c r="D1854" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1855" spans="1:4">
+      <c r="A1855" t="s">
+        <v>3691</v>
+      </c>
+      <c r="B1855" t="s">
+        <v>3692</v>
+      </c>
+      <c r="D1855" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1856" spans="1:4">
+      <c r="A1856" t="s">
+        <v>3693</v>
+      </c>
+      <c r="B1856" t="s">
+        <v>3268</v>
+      </c>
+      <c r="D1856" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1857" spans="1:4">
+      <c r="A1857" t="s">
+        <v>3694</v>
+      </c>
+      <c r="B1857" t="s">
+        <v>3695</v>
+      </c>
+      <c r="D1857" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/1/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5575" uniqueCount="3696">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5578" uniqueCount="3698">
   <si>
     <t>code</t>
   </si>
@@ -11033,6 +11033,12 @@
   </si>
   <si>
     <t>American University of Beirut</t>
+  </si>
+  <si>
+    <t>XI-IATI-CLAD</t>
+  </si>
+  <si>
+    <t>Centro Latinoamericano de Administración para el Desarrollo</t>
   </si>
   <si>
     <t>GB-CHC-1180966</t>
@@ -11433,7 +11439,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1857"/>
+  <dimension ref="A1:G1858"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -31858,7 +31864,7 @@
         <v>3693</v>
       </c>
       <c r="B1856" t="s">
-        <v>3268</v>
+        <v>3694</v>
       </c>
       <c r="D1856" t="s">
         <v>9</v>
@@ -31866,12 +31872,23 @@
     </row>
     <row r="1857" spans="1:4">
       <c r="A1857" t="s">
-        <v>3694</v>
+        <v>3695</v>
       </c>
       <c r="B1857" t="s">
-        <v>3695</v>
+        <v>3268</v>
       </c>
       <c r="D1857" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1858" spans="1:4">
+      <c r="A1858" t="s">
+        <v>3696</v>
+      </c>
+      <c r="B1858" t="s">
+        <v>3697</v>
+      </c>
+      <c r="D1858" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/1/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5578" uniqueCount="3698">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5593" uniqueCount="3708">
   <si>
     <t>code</t>
   </si>
@@ -10459,6 +10459,12 @@
     <t>Southeast Asia Freedom of Expression Network (SAFEnet)</t>
   </si>
   <si>
+    <t>IT-CF-97050280581</t>
+  </si>
+  <si>
+    <t>Comitato Internazionale per lo Sviluppo dei Popoli</t>
+  </si>
+  <si>
     <t>NG-CAC-6896199</t>
   </si>
   <si>
@@ -11099,6 +11105,30 @@
   </si>
   <si>
     <t>Eurasia Foundation</t>
+  </si>
+  <si>
+    <t>US-EIN-35-2725269</t>
+  </si>
+  <si>
+    <t>Science for Africa Foundation</t>
+  </si>
+  <si>
+    <t>UG-NGO-INDP51781129NB</t>
+  </si>
+  <si>
+    <t>RWENZORI ANTI CORRUP0TION COALITION</t>
+  </si>
+  <si>
+    <t>UA-EDR-42661077</t>
+  </si>
+  <si>
+    <t>Consumer society IMTD-INTERNATIONAL</t>
+  </si>
+  <si>
+    <t>GB-COH-00559784</t>
+  </si>
+  <si>
+    <t>The Pirbright Institute</t>
   </si>
   <si>
     <t>ET-ERCA-0056106666</t>
@@ -11439,7 +11469,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1858"/>
+  <dimension ref="A1:G1863"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -31875,7 +31905,7 @@
         <v>3695</v>
       </c>
       <c r="B1857" t="s">
-        <v>3268</v>
+        <v>3696</v>
       </c>
       <c r="D1857" t="s">
         <v>9</v>
@@ -31883,12 +31913,67 @@
     </row>
     <row r="1858" spans="1:4">
       <c r="A1858" t="s">
-        <v>3696</v>
+        <v>3697</v>
       </c>
       <c r="B1858" t="s">
-        <v>3697</v>
+        <v>3698</v>
       </c>
       <c r="D1858" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1859" spans="1:4">
+      <c r="A1859" t="s">
+        <v>3699</v>
+      </c>
+      <c r="B1859" t="s">
+        <v>3700</v>
+      </c>
+      <c r="D1859" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1860" spans="1:4">
+      <c r="A1860" t="s">
+        <v>3701</v>
+      </c>
+      <c r="B1860" t="s">
+        <v>3702</v>
+      </c>
+      <c r="D1860" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1861" spans="1:4">
+      <c r="A1861" t="s">
+        <v>3703</v>
+      </c>
+      <c r="B1861" t="s">
+        <v>3704</v>
+      </c>
+      <c r="D1861" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1862" spans="1:4">
+      <c r="A1862" t="s">
+        <v>3705</v>
+      </c>
+      <c r="B1862" t="s">
+        <v>3268</v>
+      </c>
+      <c r="D1862" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1863" spans="1:4">
+      <c r="A1863" t="s">
+        <v>3706</v>
+      </c>
+      <c r="B1863" t="s">
+        <v>3707</v>
+      </c>
+      <c r="D1863" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/1/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5593" uniqueCount="3708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5596" uniqueCount="3710">
   <si>
     <t>code</t>
   </si>
@@ -11129,6 +11129,12 @@
   </si>
   <si>
     <t>The Pirbright Institute</t>
+  </si>
+  <si>
+    <t>SE-ON-802002-3209</t>
+  </si>
+  <si>
+    <t>SMC-Faith in Development</t>
   </si>
   <si>
     <t>ET-ERCA-0056106666</t>
@@ -11469,7 +11475,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1863"/>
+  <dimension ref="A1:G1864"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -31960,7 +31966,7 @@
         <v>3705</v>
       </c>
       <c r="B1862" t="s">
-        <v>3268</v>
+        <v>3706</v>
       </c>
       <c r="D1862" t="s">
         <v>9</v>
@@ -31968,12 +31974,23 @@
     </row>
     <row r="1863" spans="1:4">
       <c r="A1863" t="s">
-        <v>3706</v>
+        <v>3707</v>
       </c>
       <c r="B1863" t="s">
-        <v>3707</v>
+        <v>3268</v>
       </c>
       <c r="D1863" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1864" spans="1:4">
+      <c r="A1864" t="s">
+        <v>3708</v>
+      </c>
+      <c r="B1864" t="s">
+        <v>3709</v>
+      </c>
+      <c r="D1864" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/1/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5596" uniqueCount="3710">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5617" uniqueCount="3724">
   <si>
     <t>code</t>
   </si>
@@ -2944,6 +2944,12 @@
     <t>Liverpool School of Tropical Medicine</t>
   </si>
   <si>
+    <t>GB-COH-RC000710</t>
+  </si>
+  <si>
+    <t>Queen Mary University of London</t>
+  </si>
+  <si>
     <t>KE-NCB-200201282375</t>
   </si>
   <si>
@@ -9991,6 +9997,12 @@
     <t>International Foundation for Electoral Systems</t>
   </si>
   <si>
+    <t>GB-COH-46049</t>
+  </si>
+  <si>
+    <t>test dave</t>
+  </si>
+  <si>
     <t>KE-KRA-P052007235U</t>
   </si>
   <si>
@@ -10327,6 +10339,12 @@
     <t>AmplifyChange</t>
   </si>
   <si>
+    <t>YE-MOPIC-0036</t>
+  </si>
+  <si>
+    <t>Partners Yemen</t>
+  </si>
+  <si>
     <t>SZ-CIT-201710132021804</t>
   </si>
   <si>
@@ -11071,6 +11089,12 @@
     <t>piermarc</t>
   </si>
   <si>
+    <t>ET-CSA-1560</t>
+  </si>
+  <si>
+    <t>Ethiopian Orthodox Church, Developement and Inter Church Aid Commssion (EOC-DICAC)</t>
+  </si>
+  <si>
     <t>KE-RCO-CPR-2014-161876</t>
   </si>
   <si>
@@ -11125,10 +11149,28 @@
     <t>Consumer society IMTD-INTERNATIONAL</t>
   </si>
   <si>
+    <t>TR-VKN-4940457659</t>
+  </si>
+  <si>
+    <t>KAMER Women's Centre Education, Production, Consultation and Solidarity Foundation</t>
+  </si>
+  <si>
     <t>GB-COH-00559784</t>
   </si>
   <si>
     <t>The Pirbright Institute</t>
+  </si>
+  <si>
+    <t>UA-EDR-38621206</t>
+  </si>
+  <si>
+    <t>Right to Protection Charitable Fund</t>
+  </si>
+  <si>
+    <t>UA-COA-44916875</t>
+  </si>
+  <si>
+    <t>СНАRITABLE ORGANIZATHION «СНАRITABLE FOUNDATHION «VERITAS SPES+ UKRAINE»</t>
   </si>
   <si>
     <t>SE-ON-802002-3209</t>
@@ -11475,7 +11517,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1864"/>
+  <dimension ref="A1:G1871"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -17985,7 +18027,7 @@
         <v>1172</v>
       </c>
       <c r="B591" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="D591" t="s">
         <v>9</v>
@@ -17993,10 +18035,10 @@
     </row>
     <row r="592" spans="1:4">
       <c r="A592" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B592" t="s">
         <v>1173</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1174</v>
       </c>
       <c r="D592" t="s">
         <v>9</v>
@@ -20625,7 +20667,7 @@
         <v>1651</v>
       </c>
       <c r="B831" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="D831" t="s">
         <v>9</v>
@@ -20633,10 +20675,10 @@
     </row>
     <row r="832" spans="1:4">
       <c r="A832" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B832" t="s">
         <v>1652</v>
-      </c>
-      <c r="B832" t="s">
-        <v>1653</v>
       </c>
       <c r="D832" t="s">
         <v>9</v>
@@ -21978,7 +22020,7 @@
         <v>1896</v>
       </c>
       <c r="B954" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="D954" t="s">
         <v>9</v>
@@ -21986,10 +22028,10 @@
     </row>
     <row r="955" spans="1:4">
       <c r="A955" t="s">
+        <v>1898</v>
+      </c>
+      <c r="B955" t="s">
         <v>1897</v>
-      </c>
-      <c r="B955" t="s">
-        <v>1898</v>
       </c>
       <c r="D955" t="s">
         <v>9</v>
@@ -24882,7 +24924,7 @@
         <v>2423</v>
       </c>
       <c r="B1218" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="D1218" t="s">
         <v>9</v>
@@ -24890,10 +24932,10 @@
     </row>
     <row r="1219" spans="1:4">
       <c r="A1219" t="s">
+        <v>2425</v>
+      </c>
+      <c r="B1219" t="s">
         <v>2424</v>
-      </c>
-      <c r="B1219" t="s">
-        <v>2425</v>
       </c>
       <c r="D1219" t="s">
         <v>9</v>
@@ -25542,7 +25584,7 @@
         <v>2542</v>
       </c>
       <c r="B1278" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="D1278" t="s">
         <v>9</v>
@@ -25550,10 +25592,10 @@
     </row>
     <row r="1279" spans="1:4">
       <c r="A1279" t="s">
+        <v>2544</v>
+      </c>
+      <c r="B1279" t="s">
         <v>2543</v>
-      </c>
-      <c r="B1279" t="s">
-        <v>2544</v>
       </c>
       <c r="D1279" t="s">
         <v>9</v>
@@ -26411,7 +26453,7 @@
         <v>2699</v>
       </c>
       <c r="B1357" t="s">
-        <v>2698</v>
+        <v>2700</v>
       </c>
       <c r="D1357" t="s">
         <v>9</v>
@@ -26419,10 +26461,10 @@
     </row>
     <row r="1358" spans="1:4">
       <c r="A1358" t="s">
+        <v>2701</v>
+      </c>
+      <c r="B1358" t="s">
         <v>2700</v>
-      </c>
-      <c r="B1358" t="s">
-        <v>2701</v>
       </c>
       <c r="D1358" t="s">
         <v>9</v>
@@ -27533,7 +27575,7 @@
         <v>2902</v>
       </c>
       <c r="B1459" t="s">
-        <v>2901</v>
+        <v>2903</v>
       </c>
       <c r="D1459" t="s">
         <v>9</v>
@@ -27541,10 +27583,10 @@
     </row>
     <row r="1460" spans="1:4">
       <c r="A1460" t="s">
+        <v>2904</v>
+      </c>
+      <c r="B1460" t="s">
         <v>2903</v>
-      </c>
-      <c r="B1460" t="s">
-        <v>2904</v>
       </c>
       <c r="D1460" t="s">
         <v>9</v>
@@ -29084,7 +29126,7 @@
         <v>3183</v>
       </c>
       <c r="B1600" t="s">
-        <v>2292</v>
+        <v>3184</v>
       </c>
       <c r="D1600" t="s">
         <v>9</v>
@@ -29092,10 +29134,10 @@
     </row>
     <row r="1601" spans="1:4">
       <c r="A1601" t="s">
-        <v>3184</v>
+        <v>3185</v>
       </c>
       <c r="B1601" t="s">
-        <v>3185</v>
+        <v>2294</v>
       </c>
       <c r="D1601" t="s">
         <v>9</v>
@@ -29326,7 +29368,7 @@
         <v>3226</v>
       </c>
       <c r="B1622" t="s">
-        <v>3217</v>
+        <v>3227</v>
       </c>
       <c r="D1622" t="s">
         <v>9</v>
@@ -29334,10 +29376,10 @@
     </row>
     <row r="1623" spans="1:4">
       <c r="A1623" t="s">
-        <v>3227</v>
+        <v>3228</v>
       </c>
       <c r="B1623" t="s">
-        <v>3228</v>
+        <v>3219</v>
       </c>
       <c r="D1623" t="s">
         <v>9</v>
@@ -31977,7 +32019,7 @@
         <v>3707</v>
       </c>
       <c r="B1863" t="s">
-        <v>3268</v>
+        <v>3708</v>
       </c>
       <c r="D1863" t="s">
         <v>9</v>
@@ -31985,12 +32027,89 @@
     </row>
     <row r="1864" spans="1:4">
       <c r="A1864" t="s">
-        <v>3708</v>
+        <v>3709</v>
       </c>
       <c r="B1864" t="s">
-        <v>3709</v>
+        <v>3710</v>
       </c>
       <c r="D1864" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1865" spans="1:4">
+      <c r="A1865" t="s">
+        <v>3711</v>
+      </c>
+      <c r="B1865" t="s">
+        <v>3712</v>
+      </c>
+      <c r="D1865" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1866" spans="1:4">
+      <c r="A1866" t="s">
+        <v>3713</v>
+      </c>
+      <c r="B1866" t="s">
+        <v>3714</v>
+      </c>
+      <c r="D1866" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1867" spans="1:4">
+      <c r="A1867" t="s">
+        <v>3715</v>
+      </c>
+      <c r="B1867" t="s">
+        <v>3716</v>
+      </c>
+      <c r="D1867" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1868" spans="1:4">
+      <c r="A1868" t="s">
+        <v>3717</v>
+      </c>
+      <c r="B1868" t="s">
+        <v>3718</v>
+      </c>
+      <c r="D1868" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1869" spans="1:4">
+      <c r="A1869" t="s">
+        <v>3719</v>
+      </c>
+      <c r="B1869" t="s">
+        <v>3720</v>
+      </c>
+      <c r="D1869" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1870" spans="1:4">
+      <c r="A1870" t="s">
+        <v>3721</v>
+      </c>
+      <c r="B1870" t="s">
+        <v>3270</v>
+      </c>
+      <c r="D1870" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1871" spans="1:4">
+      <c r="A1871" t="s">
+        <v>3722</v>
+      </c>
+      <c r="B1871" t="s">
+        <v>3723</v>
+      </c>
+      <c r="D1871" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/1/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6328" uniqueCount="4195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6337" uniqueCount="4201">
   <si>
     <t>code</t>
   </si>
@@ -12193,6 +12193,12 @@
     <t>Rift Partners GmbH</t>
   </si>
   <si>
+    <t>TZ-NNCB-06NGO-00010000</t>
+  </si>
+  <si>
+    <t>Endeleza Wazee Kigoma (EWAKI)</t>
+  </si>
+  <si>
     <t>GB-GOV-28</t>
   </si>
   <si>
@@ -12277,6 +12283,12 @@
     <t>Partners In Health</t>
   </si>
   <si>
+    <t>US-SAM-P8V7YEC1GN34</t>
+  </si>
+  <si>
+    <t>Pangea Africa Ltd</t>
+  </si>
+  <si>
     <t>CR-RPJ-3-002-248583</t>
   </si>
   <si>
@@ -12329,6 +12341,12 @@
   </si>
   <si>
     <t>Rapid Asia Co., Ltd.</t>
+  </si>
+  <si>
+    <t>PK-VSWA-2172-2003</t>
+  </si>
+  <si>
+    <t>IDEA (Initiative for Development &amp; Empowerment Axis)</t>
   </si>
   <si>
     <t>SE-ON-802426-1664</t>
@@ -12930,7 +12948,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2108"/>
+  <dimension ref="A1:G2111"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -35698,7 +35716,7 @@
         <v>4117</v>
       </c>
       <c r="B2069" t="s">
-        <v>2888</v>
+        <v>4118</v>
       </c>
       <c r="D2069" t="s">
         <v>9</v>
@@ -35706,10 +35724,10 @@
     </row>
     <row r="2070" spans="1:4">
       <c r="A2070" t="s">
-        <v>4118</v>
+        <v>4119</v>
       </c>
       <c r="B2070" t="s">
-        <v>4119</v>
+        <v>4120</v>
       </c>
       <c r="D2070" t="s">
         <v>9</v>
@@ -35717,10 +35735,10 @@
     </row>
     <row r="2071" spans="1:4">
       <c r="A2071" t="s">
-        <v>4120</v>
+        <v>4121</v>
       </c>
       <c r="B2071" t="s">
-        <v>4121</v>
+        <v>4122</v>
       </c>
       <c r="D2071" t="s">
         <v>9</v>
@@ -35728,10 +35746,10 @@
     </row>
     <row r="2072" spans="1:4">
       <c r="A2072" t="s">
-        <v>4122</v>
+        <v>4123</v>
       </c>
       <c r="B2072" t="s">
-        <v>4123</v>
+        <v>2888</v>
       </c>
       <c r="D2072" t="s">
         <v>9</v>
@@ -36116,7 +36134,7 @@
         <v>4192</v>
       </c>
       <c r="B2107" t="s">
-        <v>3283</v>
+        <v>4193</v>
       </c>
       <c r="D2107" t="s">
         <v>9</v>
@@ -36124,12 +36142,45 @@
     </row>
     <row r="2108" spans="1:4">
       <c r="A2108" t="s">
-        <v>4193</v>
+        <v>4194</v>
       </c>
       <c r="B2108" t="s">
-        <v>4194</v>
+        <v>4195</v>
       </c>
       <c r="D2108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:4">
+      <c r="A2109" t="s">
+        <v>4196</v>
+      </c>
+      <c r="B2109" t="s">
+        <v>4197</v>
+      </c>
+      <c r="D2109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:4">
+      <c r="A2110" t="s">
+        <v>4198</v>
+      </c>
+      <c r="B2110" t="s">
+        <v>3283</v>
+      </c>
+      <c r="D2110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:4">
+      <c r="A2111" t="s">
+        <v>4199</v>
+      </c>
+      <c r="B2111" t="s">
+        <v>4200</v>
+      </c>
+      <c r="D2111" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/1/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6337" uniqueCount="4201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6382" uniqueCount="4231">
   <si>
     <t>code</t>
   </si>
@@ -3064,7 +3064,7 @@
     <t>FR-SIRET-77566669600015</t>
   </si>
   <si>
-    <t>SECOURS CATHOLIQUE - CARITAS FRANCE</t>
+    <t>Secours Catholique - Caritas France</t>
   </si>
   <si>
     <t>GB-CHC-1062638</t>
@@ -6079,7 +6079,7 @@
     <t>NL-KVK-27367015</t>
   </si>
   <si>
-    <t>Netherlands Organisation for Scientific Research (NWO)</t>
+    <t>Dutch Research Council (NWO)</t>
   </si>
   <si>
     <t>US-EIN-13-3377893</t>
@@ -10999,7 +10999,7 @@
     <t>XM-OCHA-HPC6052</t>
   </si>
   <si>
-    <t>Himilo Relief and Development Association (HIRDA)</t>
+    <t>Himilo Relief and Development Association （HIRDA Somalia）</t>
   </si>
   <si>
     <t>BE-BCE_KBO-0665.649.335</t>
@@ -12223,6 +12223,18 @@
     <t>Africa Research &amp; Impact Network (ARIN)</t>
   </si>
   <si>
+    <t>IN-MHA-231660448</t>
+  </si>
+  <si>
+    <t>CENTRE FOR CHRONIC DISEASE CONTROL</t>
+  </si>
+  <si>
+    <t>TG-NIF-1000047187</t>
+  </si>
+  <si>
+    <t>Women in Law and Development in Africa-Afrique de l’Ouest (WiLDAF-AO)</t>
+  </si>
+  <si>
     <t>CH-FDJP-CHE365512867</t>
   </si>
   <si>
@@ -12247,6 +12259,54 @@
     <t>ADRA Sweden</t>
   </si>
   <si>
+    <t>GB-COH-07921860</t>
+  </si>
+  <si>
+    <t>Institutional Investors Group on Climate Change</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-100493543</t>
+  </si>
+  <si>
+    <t>Associaçao de Protecao do Idosos de Tete</t>
+  </si>
+  <si>
+    <t>GB-COH-12075030</t>
+  </si>
+  <si>
+    <t>Impact Knowledge Limited T/A Impact Capital Africa</t>
+  </si>
+  <si>
+    <t>GB-CHC-1111719</t>
+  </si>
+  <si>
+    <t>Anglo American Foundation</t>
+  </si>
+  <si>
+    <t>TZ-NNCB-00NGO00009862</t>
+  </si>
+  <si>
+    <t>Mtandao wa vikundi vya wakulima na wafugaji Nyancha</t>
+  </si>
+  <si>
+    <t>UA-EDR-45583070</t>
+  </si>
+  <si>
+    <t>VRUNA</t>
+  </si>
+  <si>
+    <t>XI-ROR-01ej9dk98</t>
+  </si>
+  <si>
+    <t>University of Melbourne</t>
+  </si>
+  <si>
+    <t>TH-MOI-KhorThor3005</t>
+  </si>
+  <si>
+    <t>Thai Lawyers for Human Rights</t>
+  </si>
+  <si>
     <t>SE-ON-252002-6135</t>
   </si>
   <si>
@@ -12287,6 +12347,36 @@
   </si>
   <si>
     <t>Pangea Africa Ltd</t>
+  </si>
+  <si>
+    <t>ZA-CIP-2025-956558-08</t>
+  </si>
+  <si>
+    <t>Impact Finance Facility NPC</t>
+  </si>
+  <si>
+    <t>ZA-CIT-9063151162</t>
+  </si>
+  <si>
+    <t>University of KwaZulu-Natal</t>
+  </si>
+  <si>
+    <t>MZ-MOJ-821-B</t>
+  </si>
+  <si>
+    <t>Diocese dos Libombos - ASA</t>
+  </si>
+  <si>
+    <t>BR-CNPJ-01567601-0001-43</t>
+  </si>
+  <si>
+    <t>Universidade Federal de Goiás</t>
+  </si>
+  <si>
+    <t>ET-CSA-0067</t>
+  </si>
+  <si>
+    <t>Tesfa Social &amp; Development Association</t>
   </si>
   <si>
     <t>CR-RPJ-3-002-248583</t>
@@ -12948,7 +13038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2111"/>
+  <dimension ref="A1:G2126"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -35749,7 +35839,7 @@
         <v>4123</v>
       </c>
       <c r="B2072" t="s">
-        <v>2888</v>
+        <v>4124</v>
       </c>
       <c r="D2072" t="s">
         <v>9</v>
@@ -35757,10 +35847,10 @@
     </row>
     <row r="2073" spans="1:4">
       <c r="A2073" t="s">
-        <v>4124</v>
+        <v>4125</v>
       </c>
       <c r="B2073" t="s">
-        <v>4125</v>
+        <v>4126</v>
       </c>
       <c r="D2073" t="s">
         <v>9</v>
@@ -35768,10 +35858,10 @@
     </row>
     <row r="2074" spans="1:4">
       <c r="A2074" t="s">
-        <v>4126</v>
+        <v>4127</v>
       </c>
       <c r="B2074" t="s">
-        <v>4127</v>
+        <v>4128</v>
       </c>
       <c r="D2074" t="s">
         <v>9</v>
@@ -35779,10 +35869,10 @@
     </row>
     <row r="2075" spans="1:4">
       <c r="A2075" t="s">
-        <v>4128</v>
+        <v>4129</v>
       </c>
       <c r="B2075" t="s">
-        <v>4129</v>
+        <v>4130</v>
       </c>
       <c r="D2075" t="s">
         <v>9</v>
@@ -35790,10 +35880,10 @@
     </row>
     <row r="2076" spans="1:4">
       <c r="A2076" t="s">
-        <v>4130</v>
+        <v>4131</v>
       </c>
       <c r="B2076" t="s">
-        <v>4131</v>
+        <v>4132</v>
       </c>
       <c r="D2076" t="s">
         <v>9</v>
@@ -35801,10 +35891,10 @@
     </row>
     <row r="2077" spans="1:4">
       <c r="A2077" t="s">
-        <v>4132</v>
+        <v>4133</v>
       </c>
       <c r="B2077" t="s">
-        <v>4133</v>
+        <v>4134</v>
       </c>
       <c r="D2077" t="s">
         <v>9</v>
@@ -35812,10 +35902,10 @@
     </row>
     <row r="2078" spans="1:4">
       <c r="A2078" t="s">
-        <v>4134</v>
+        <v>4135</v>
       </c>
       <c r="B2078" t="s">
-        <v>4135</v>
+        <v>4136</v>
       </c>
       <c r="D2078" t="s">
         <v>9</v>
@@ -35823,10 +35913,10 @@
     </row>
     <row r="2079" spans="1:4">
       <c r="A2079" t="s">
-        <v>4136</v>
+        <v>4137</v>
       </c>
       <c r="B2079" t="s">
-        <v>4137</v>
+        <v>4138</v>
       </c>
       <c r="D2079" t="s">
         <v>9</v>
@@ -35834,10 +35924,10 @@
     </row>
     <row r="2080" spans="1:4">
       <c r="A2080" t="s">
-        <v>4138</v>
+        <v>4139</v>
       </c>
       <c r="B2080" t="s">
-        <v>4139</v>
+        <v>4140</v>
       </c>
       <c r="D2080" t="s">
         <v>9</v>
@@ -35845,10 +35935,10 @@
     </row>
     <row r="2081" spans="1:4">
       <c r="A2081" t="s">
-        <v>4140</v>
+        <v>4141</v>
       </c>
       <c r="B2081" t="s">
-        <v>4141</v>
+        <v>4142</v>
       </c>
       <c r="D2081" t="s">
         <v>9</v>
@@ -35856,10 +35946,10 @@
     </row>
     <row r="2082" spans="1:4">
       <c r="A2082" t="s">
-        <v>4142</v>
+        <v>4143</v>
       </c>
       <c r="B2082" t="s">
-        <v>4143</v>
+        <v>4144</v>
       </c>
       <c r="D2082" t="s">
         <v>9</v>
@@ -35867,10 +35957,10 @@
     </row>
     <row r="2083" spans="1:4">
       <c r="A2083" t="s">
-        <v>4144</v>
+        <v>4145</v>
       </c>
       <c r="B2083" t="s">
-        <v>4145</v>
+        <v>4146</v>
       </c>
       <c r="D2083" t="s">
         <v>9</v>
@@ -35878,10 +35968,10 @@
     </row>
     <row r="2084" spans="1:4">
       <c r="A2084" t="s">
-        <v>4146</v>
+        <v>4147</v>
       </c>
       <c r="B2084" t="s">
-        <v>4147</v>
+        <v>4148</v>
       </c>
       <c r="D2084" t="s">
         <v>9</v>
@@ -35889,10 +35979,10 @@
     </row>
     <row r="2085" spans="1:4">
       <c r="A2085" t="s">
-        <v>4148</v>
+        <v>4149</v>
       </c>
       <c r="B2085" t="s">
-        <v>4149</v>
+        <v>4150</v>
       </c>
       <c r="D2085" t="s">
         <v>9</v>
@@ -35900,10 +35990,10 @@
     </row>
     <row r="2086" spans="1:4">
       <c r="A2086" t="s">
-        <v>4150</v>
+        <v>4151</v>
       </c>
       <c r="B2086" t="s">
-        <v>4151</v>
+        <v>4152</v>
       </c>
       <c r="D2086" t="s">
         <v>9</v>
@@ -35911,10 +36001,10 @@
     </row>
     <row r="2087" spans="1:4">
       <c r="A2087" t="s">
-        <v>4152</v>
+        <v>4153</v>
       </c>
       <c r="B2087" t="s">
-        <v>4153</v>
+        <v>2888</v>
       </c>
       <c r="D2087" t="s">
         <v>9</v>
@@ -36167,7 +36257,7 @@
         <v>4198</v>
       </c>
       <c r="B2110" t="s">
-        <v>3283</v>
+        <v>4199</v>
       </c>
       <c r="D2110" t="s">
         <v>9</v>
@@ -36175,12 +36265,177 @@
     </row>
     <row r="2111" spans="1:4">
       <c r="A2111" t="s">
-        <v>4199</v>
+        <v>4200</v>
       </c>
       <c r="B2111" t="s">
-        <v>4200</v>
+        <v>4201</v>
       </c>
       <c r="D2111" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:4">
+      <c r="A2112" t="s">
+        <v>4202</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>4203</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:4">
+      <c r="A2113" t="s">
+        <v>4204</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>4205</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:4">
+      <c r="A2114" t="s">
+        <v>4206</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>4207</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:4">
+      <c r="A2115" t="s">
+        <v>4208</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>4209</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:4">
+      <c r="A2116" t="s">
+        <v>4210</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>4211</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:4">
+      <c r="A2117" t="s">
+        <v>4212</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>4213</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:4">
+      <c r="A2118" t="s">
+        <v>4214</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>4215</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:4">
+      <c r="A2119" t="s">
+        <v>4216</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>4217</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:4">
+      <c r="A2120" t="s">
+        <v>4218</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>4219</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:4">
+      <c r="A2121" t="s">
+        <v>4220</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>4221</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:4">
+      <c r="A2122" t="s">
+        <v>4222</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>4223</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:4">
+      <c r="A2123" t="s">
+        <v>4224</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>4225</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:4">
+      <c r="A2124" t="s">
+        <v>4226</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>4227</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:4">
+      <c r="A2125" t="s">
+        <v>4228</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>3283</v>
+      </c>
+      <c r="D2125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:4">
+      <c r="A2126" t="s">
+        <v>4229</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>4230</v>
+      </c>
+      <c r="D2126" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/1/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6382" uniqueCount="4231">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6388" uniqueCount="4235">
   <si>
     <t>code</t>
   </si>
@@ -12500,6 +12500,18 @@
   </si>
   <si>
     <t>Worlds Childrens Prize Foundation</t>
+  </si>
+  <si>
+    <t>GB-COH-954616</t>
+  </si>
+  <si>
+    <t>Institute for Fiscal Studies</t>
+  </si>
+  <si>
+    <t>PH-SEC-0000186387</t>
+  </si>
+  <si>
+    <t>Caucus of Development NGO Networks Inc.</t>
   </si>
   <si>
     <t>PH-SEC-AN96001837</t>
@@ -13038,7 +13050,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2126"/>
+  <dimension ref="A1:G2128"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -36422,7 +36434,7 @@
         <v>4228</v>
       </c>
       <c r="B2125" t="s">
-        <v>3283</v>
+        <v>4229</v>
       </c>
       <c r="D2125" t="s">
         <v>9</v>
@@ -36430,12 +36442,34 @@
     </row>
     <row r="2126" spans="1:4">
       <c r="A2126" t="s">
-        <v>4229</v>
+        <v>4230</v>
       </c>
       <c r="B2126" t="s">
-        <v>4230</v>
+        <v>4231</v>
       </c>
       <c r="D2126" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:4">
+      <c r="A2127" t="s">
+        <v>4232</v>
+      </c>
+      <c r="B2127" t="s">
+        <v>3283</v>
+      </c>
+      <c r="D2127" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:4">
+      <c r="A2128" t="s">
+        <v>4233</v>
+      </c>
+      <c r="B2128" t="s">
+        <v>4234</v>
+      </c>
+      <c r="D2128" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/1/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6388" uniqueCount="4235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6412" uniqueCount="4251">
   <si>
     <t>code</t>
   </si>
@@ -12508,6 +12508,18 @@
     <t>Institute for Fiscal Studies</t>
   </si>
   <si>
+    <t>MM-MHA-0004-1951</t>
+  </si>
+  <si>
+    <t>Myanmar Baptist Churches Union</t>
+  </si>
+  <si>
+    <t>CR-RPJ-300304509309</t>
+  </si>
+  <si>
+    <t>Centro Agronómico Tropical de Investigación y Enseñanza-CATIE</t>
+  </si>
+  <si>
     <t>PH-SEC-0000186387</t>
   </si>
   <si>
@@ -12532,6 +12544,30 @@
     <t>National Association For Popular Action (AMEL)</t>
   </si>
   <si>
+    <t>KE-NCB-21805120120102</t>
+  </si>
+  <si>
+    <t>Action For Sustainability Initiative</t>
+  </si>
+  <si>
+    <t>KE-NCB-218051200902226007</t>
+  </si>
+  <si>
+    <t>CENTRE FOR HUMAN RIGHTS AND POLICY STUDIES</t>
+  </si>
+  <si>
+    <t>KE-RCO-CPR-2013-112912</t>
+  </si>
+  <si>
+    <t>EED Advisory Limited</t>
+  </si>
+  <si>
+    <t>IN-MHA-231660424</t>
+  </si>
+  <si>
+    <t>Integrated Research and Action For Developement</t>
+  </si>
+  <si>
     <t>GH-TIN-V0004994299</t>
   </si>
   <si>
@@ -12542,6 +12578,18 @@
   </si>
   <si>
     <t>Sierra Leone Urban Research Centre (SLURC)</t>
+  </si>
+  <si>
+    <t>XI-ROR-05m2fqn25</t>
+  </si>
+  <si>
+    <t>Chiang Mai University</t>
+  </si>
+  <si>
+    <t>CH-FDJP-CHE-207616410</t>
+  </si>
+  <si>
+    <t>Centre on Armed Groups</t>
   </si>
   <si>
     <t>GB-CHC-1193984</t>
@@ -13050,7 +13098,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2128"/>
+  <dimension ref="A1:G2136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -36456,7 +36504,7 @@
         <v>4232</v>
       </c>
       <c r="B2127" t="s">
-        <v>3283</v>
+        <v>4233</v>
       </c>
       <c r="D2127" t="s">
         <v>9</v>
@@ -36464,12 +36512,100 @@
     </row>
     <row r="2128" spans="1:4">
       <c r="A2128" t="s">
-        <v>4233</v>
+        <v>4234</v>
       </c>
       <c r="B2128" t="s">
-        <v>4234</v>
+        <v>4235</v>
       </c>
       <c r="D2128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2129" spans="1:4">
+      <c r="A2129" t="s">
+        <v>4236</v>
+      </c>
+      <c r="B2129" t="s">
+        <v>4237</v>
+      </c>
+      <c r="D2129" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2130" spans="1:4">
+      <c r="A2130" t="s">
+        <v>4238</v>
+      </c>
+      <c r="B2130" t="s">
+        <v>4239</v>
+      </c>
+      <c r="D2130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2131" spans="1:4">
+      <c r="A2131" t="s">
+        <v>4240</v>
+      </c>
+      <c r="B2131" t="s">
+        <v>4241</v>
+      </c>
+      <c r="D2131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2132" spans="1:4">
+      <c r="A2132" t="s">
+        <v>4242</v>
+      </c>
+      <c r="B2132" t="s">
+        <v>4243</v>
+      </c>
+      <c r="D2132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2133" spans="1:4">
+      <c r="A2133" t="s">
+        <v>4244</v>
+      </c>
+      <c r="B2133" t="s">
+        <v>4245</v>
+      </c>
+      <c r="D2133" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2134" spans="1:4">
+      <c r="A2134" t="s">
+        <v>4246</v>
+      </c>
+      <c r="B2134" t="s">
+        <v>4247</v>
+      </c>
+      <c r="D2134" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2135" spans="1:4">
+      <c r="A2135" t="s">
+        <v>4248</v>
+      </c>
+      <c r="B2135" t="s">
+        <v>3283</v>
+      </c>
+      <c r="D2135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2136" spans="1:4">
+      <c r="A2136" t="s">
+        <v>4249</v>
+      </c>
+      <c r="B2136" t="s">
+        <v>4250</v>
+      </c>
+      <c r="D2136" t="s">
         <v>9</v>
       </c>
     </row>

--- a/api/1/clv1/codelist/ReportingOrganisation.xlsx
+++ b/api/1/clv1/codelist/ReportingOrganisation.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6412" uniqueCount="4251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6415" uniqueCount="4253">
   <si>
     <t>code</t>
   </si>
@@ -2080,7 +2080,7 @@
     <t>NL-KVK-30285304</t>
   </si>
   <si>
-    <t>Stichting Humana</t>
+    <t>Sympany+</t>
   </si>
   <si>
     <t>GB-CHC-1148404</t>
@@ -12584,6 +12584,12 @@
   </si>
   <si>
     <t>Chiang Mai University</t>
+  </si>
+  <si>
+    <t>GB-UKPRN-10004180</t>
+  </si>
+  <si>
+    <t>Manchester Metropolitan University</t>
   </si>
   <si>
     <t>CH-FDJP-CHE-207616410</t>
@@ -13098,7 +13104,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2136"/>
+  <dimension ref="A1:G2137"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -36592,7 +36598,7 @@
         <v>4248</v>
       </c>
       <c r="B2135" t="s">
-        <v>3283</v>
+        <v>4249</v>
       </c>
       <c r="D2135" t="s">
         <v>9</v>
@@ -36600,12 +36606,23 @@
     </row>
     <row r="2136" spans="1:4">
       <c r="A2136" t="s">
-        <v>4249</v>
+        <v>4250</v>
       </c>
       <c r="B2136" t="s">
-        <v>4250</v>
+        <v>3283</v>
       </c>
       <c r="D2136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2137" spans="1:4">
+      <c r="A2137" t="s">
+        <v>4251</v>
+      </c>
+      <c r="B2137" t="s">
+        <v>4252</v>
+      </c>
+      <c r="D2137" t="s">
         <v>9</v>
       </c>
     </row>
